--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487555_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487555_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.9264</v>
+        <v>1.8881</v>
       </c>
       <c r="E2" t="n">
-        <v>1.577</v>
+        <v>0.6724</v>
       </c>
       <c r="F2" t="n">
-        <v>1.3494</v>
+        <v>1.2157</v>
       </c>
       <c r="G2" t="n">
         <v>1.2573</v>
@@ -610,13 +610,13 @@
         <v>1.3709</v>
       </c>
       <c r="S2" t="n">
-        <v>1.2577</v>
+        <v>0.2195</v>
       </c>
       <c r="T2" t="n">
-        <v>1.2086</v>
+        <v>0.3041</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0491</v>
+        <v>-0.08450000000000001</v>
       </c>
       <c r="V2" t="n">
         <v>0.9988</v>
@@ -643,10 +643,10 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.2903</v>
+        <v>1.3497</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2973</v>
+        <v>0.3567</v>
       </c>
       <c r="F3" t="n">
         <v>0.993</v>
@@ -688,10 +688,10 @@
         <v>0.7834</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0594</v>
+        <v>0.1188</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2664</v>
+        <v>0.3258</v>
       </c>
       <c r="U3" t="n">
         <v>-0.207</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. LUIS</t>
+          <t>M. RODRIGUEZ ALVAREZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7923</v>
+        <v>0.4277</v>
       </c>
       <c r="E4" t="n">
-        <v>1.1423</v>
+        <v>1.8414</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.35</v>
+        <v>-1.4136</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5491</v>
+        <v>-0.8035</v>
       </c>
       <c r="H4" t="n">
-        <v>1.918</v>
+        <v>0.7779</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.3689</v>
+        <v>-1.5814</v>
       </c>
       <c r="J4" t="n">
-        <v>2.1522</v>
+        <v>0.6642</v>
       </c>
       <c r="K4" t="n">
-        <v>2.1878</v>
+        <v>0.7758</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.0356</v>
+        <v>-0.1116</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.6031</v>
+        <v>-1.4677</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.2698</v>
+        <v>0.0021</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.3333</v>
+        <v>-1.4698</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1958</v>
+        <v>0.9792</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9792</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.1751</v>
+        <v>0.9792</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5406</v>
+        <v>0.252</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0306</v>
+        <v>-0.0394</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5711000000000001</v>
+        <v>0.2914</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.4931</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.2166</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.4931</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. RODRIGUEZ ALVAREZ</t>
+          <t>J. LUIS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4126</v>
+        <v>0.2996</v>
       </c>
       <c r="E5" t="n">
-        <v>1.9866</v>
+        <v>0.9971</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.574</v>
+        <v>-0.6975</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.8035</v>
+        <v>0.5491</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7779</v>
+        <v>1.918</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.5814</v>
+        <v>-1.3689</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6642</v>
+        <v>2.1522</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7758</v>
+        <v>2.1878</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.1116</v>
+        <v>-0.0356</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.4677</v>
+        <v>-1.6031</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0021</v>
+        <v>-0.2698</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.4698</v>
+        <v>-1.3333</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9792</v>
+        <v>0.1958</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.9792</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9792</v>
+        <v>1.1751</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2369</v>
+        <v>0.0478</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1059</v>
+        <v>-0.1759</v>
       </c>
       <c r="U5" t="n">
-        <v>0.131</v>
+        <v>0.2236</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.4931</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2166</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.2166</v>
+        <v>-0.4931</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C. MONTERO MECA</t>
+          <t>C. NOGUEROL BARRENECHEA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.614</v>
+        <v>-0.4382</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.8182</v>
+        <v>0.7432</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2042</v>
+        <v>-1.1813</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.9108000000000001</v>
+        <v>-4.2989</v>
       </c>
       <c r="H6" t="n">
-        <v>0.13</v>
+        <v>-1.1614</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.0408</v>
+        <v>-3.1375</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.5806</v>
+        <v>-1.8188</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0612</v>
+        <v>0.2635</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.6418</v>
+        <v>-2.0823</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.3302</v>
+        <v>-2.4801</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0687</v>
+        <v>-1.4249</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.399</v>
+        <v>-1.0552</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3917</v>
+        <v>-0.3917</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.9585</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3917</v>
+        <v>1.5668</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0949</v>
+        <v>0.2697</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2376</v>
+        <v>0.2623</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1427</v>
+        <v>0.0074</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>3.9828</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>4.2581</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>C. NOGUEROL BARRENECHEA</t>
+          <t>C. MONTERO MECA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.6338</v>
+        <v>-0.6407</v>
       </c>
       <c r="E7" t="n">
+        <v>-0.8182</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.1775</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-0.9108000000000001</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-1.0408</v>
+      </c>
+      <c r="J7" t="n">
+        <v>-0.5806</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.0612</v>
+      </c>
+      <c r="L7" t="n">
+        <v>-0.6418</v>
+      </c>
+      <c r="M7" t="n">
+        <v>-0.3302</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.0687</v>
+      </c>
+      <c r="O7" t="n">
         <v>-0.399</v>
       </c>
-      <c r="F7" t="n">
-        <v>-1.2348</v>
-      </c>
-      <c r="G7" t="n">
-        <v>-4.2989</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-1.1614</v>
-      </c>
-      <c r="I7" t="n">
-        <v>-3.1375</v>
-      </c>
-      <c r="J7" t="n">
-        <v>-1.8188</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0.2635</v>
-      </c>
-      <c r="L7" t="n">
-        <v>-2.0823</v>
-      </c>
-      <c r="M7" t="n">
-        <v>-2.4801</v>
-      </c>
-      <c r="N7" t="n">
-        <v>-1.4249</v>
-      </c>
-      <c r="O7" t="n">
-        <v>-1.0552</v>
-      </c>
       <c r="P7" t="n">
-        <v>-0.3917</v>
+        <v>0.3917</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.9585</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5668</v>
+        <v>0.3917</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.926</v>
+        <v>-0.1216</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8799</v>
+        <v>-0.2376</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0461</v>
+        <v>0.116</v>
       </c>
       <c r="V7" t="n">
-        <v>3.9828</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>4.2581</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2754</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.6906</v>
+        <v>-0.8892</v>
       </c>
       <c r="E8" t="n">
-        <v>1.3896</v>
+        <v>1.9771</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.0801</v>
+        <v>-2.8663</v>
       </c>
       <c r="G8" t="n">
         <v>-3.2543</v>
@@ -1078,13 +1078,13 @@
         <v>1.3709</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7485000000000001</v>
+        <v>0.0529</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1382</v>
+        <v>0.4493</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.6102</v>
+        <v>-0.3964</v>
       </c>
       <c r="V8" t="n">
         <v>0.9412</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.8675</v>
+        <v>-1.7311</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.7047</v>
+        <v>-1.3812</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1628</v>
+        <v>-0.3499</v>
       </c>
       <c r="G9" t="n">
         <v>-2.6257</v>
@@ -1156,13 +1156,13 @@
         <v>1.7626</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4034</v>
+        <v>0.5397999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2923</v>
+        <v>0.0312</v>
       </c>
       <c r="U9" t="n">
-        <v>0.6957</v>
+        <v>0.5086000000000001</v>
       </c>
       <c r="V9" t="n">
         <v>0.5507</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.7167</v>
+        <v>-3.869</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.1984</v>
+        <v>-2.5913</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.5182</v>
+        <v>-1.2776</v>
       </c>
       <c r="G10" t="n">
         <v>-3.8688</v>
@@ -1234,13 +1234,13 @@
         <v>1.3709</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0484</v>
+        <v>-0.2007</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2294</v>
+        <v>-0.1635</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2778</v>
+        <v>-0.0372</v>
       </c>
       <c r="V10" t="n">
         <v>1.7673</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.3421</v>
+        <v>-3.9489</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.0893</v>
+        <v>-1.7229</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.2527</v>
+        <v>-2.226</v>
       </c>
       <c r="G11" t="n">
         <v>-2.7098</v>
@@ -1312,13 +1312,13 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4156</v>
+        <v>-0.0225</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1847</v>
+        <v>0.1817</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.231</v>
+        <v>-0.2042</v>
       </c>
       <c r="V11" t="n">
         <v>-1.2166</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-8.443099999999999</v>
+        <v>-7.552</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.8168000000000006</v>
+        <v>0.07429999999999959</v>
       </c>
       <c r="F12" t="n">
-        <v>-7.625999999999999</v>
+        <v>-7.626</v>
       </c>
       <c r="G12" t="n">
         <v>-16.2179</v>
@@ -1390,13 +1390,13 @@
         <v>10.7715</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2645999999999997</v>
+        <v>1.1557</v>
       </c>
       <c r="T12" t="n">
-        <v>0.04699999999999974</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2175000000000001</v>
+        <v>0.2177000000000001</v>
       </c>
       <c r="V12" t="n">
         <v>6.5311</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.5001</v>
+        <v>7.1454</v>
       </c>
       <c r="E13" t="n">
-        <v>4.6779</v>
+        <v>4.7802</v>
       </c>
       <c r="F13" t="n">
-        <v>1.8222</v>
+        <v>2.3652</v>
       </c>
       <c r="G13" t="n">
         <v>3.4317</v>
@@ -1468,13 +1468,13 @@
         <v>1.9585</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.1067</v>
+        <v>0.5386</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4882</v>
+        <v>-0.3858</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3814</v>
+        <v>0.9244</v>
       </c>
       <c r="V13" t="n">
         <v>1.2166</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.8052</v>
+        <v>6.0394</v>
       </c>
       <c r="E14" t="n">
-        <v>4.4676</v>
+        <v>4.6723</v>
       </c>
       <c r="F14" t="n">
-        <v>1.3376</v>
+        <v>1.3672</v>
       </c>
       <c r="G14" t="n">
         <v>3.3203</v>
@@ -1546,13 +1546,13 @@
         <v>1.5668</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.0231</v>
+        <v>0.2111</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2506</v>
+        <v>-0.0459</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2275</v>
+        <v>0.257</v>
       </c>
       <c r="V14" t="n">
         <v>0.9412</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.3964</v>
+        <v>4.9745</v>
       </c>
       <c r="E15" t="n">
-        <v>3.7822</v>
+        <v>4.1915</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6142</v>
+        <v>0.7829</v>
       </c>
       <c r="G15" t="n">
         <v>3.4847</v>
@@ -1624,13 +1624,13 @@
         <v>0.3917</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.3256</v>
+        <v>0.2525</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.5346</v>
+        <v>-0.1253</v>
       </c>
       <c r="U15" t="n">
-        <v>0.209</v>
+        <v>0.3777</v>
       </c>
       <c r="V15" t="n">
         <v>1.8249</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>O. KOUROUMA</t>
+          <t>L. MC-CARTHY SANTOS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.4804</v>
+        <v>1.392</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.1322</v>
+        <v>0.6264999999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>2.6126</v>
+        <v>0.7655</v>
       </c>
       <c r="G16" t="n">
-        <v>2.5641</v>
+        <v>1.8074</v>
       </c>
       <c r="H16" t="n">
-        <v>1.3257</v>
+        <v>-1.8759</v>
       </c>
       <c r="I16" t="n">
-        <v>1.2384</v>
+        <v>3.6833</v>
       </c>
       <c r="J16" t="n">
-        <v>1.857</v>
+        <v>1.6492</v>
       </c>
       <c r="K16" t="n">
-        <v>2.135</v>
+        <v>-1.0634</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.2781</v>
+        <v>2.7126</v>
       </c>
       <c r="M16" t="n">
-        <v>0.7072000000000001</v>
+        <v>0.1583</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.8093</v>
+        <v>-0.8124</v>
       </c>
       <c r="O16" t="n">
-        <v>1.5165</v>
+        <v>0.9707</v>
       </c>
       <c r="P16" t="n">
+        <v>0.3917</v>
+      </c>
+      <c r="Q16" t="n">
         <v>-0.9792</v>
       </c>
-      <c r="Q16" t="n">
-        <v>-2.9377</v>
-      </c>
       <c r="R16" t="n">
-        <v>1.9585</v>
+        <v>1.3709</v>
       </c>
       <c r="S16" t="n">
-        <v>2.2848</v>
+        <v>0.1341</v>
       </c>
       <c r="T16" t="n">
-        <v>2.0626</v>
+        <v>-0.3188</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2223</v>
+        <v>0.4529</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.3894</v>
+        <v>-0.9412</v>
       </c>
       <c r="W16" t="n">
-        <v>-1.114</v>
+        <v>0.2754</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2754</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>L. MC-CARTHY SANTOS</t>
+          <t>O. KOUROUMA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9328</v>
+        <v>1.304</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0125</v>
+        <v>-1.6672</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9203</v>
+        <v>2.9712</v>
       </c>
       <c r="G17" t="n">
-        <v>1.8074</v>
+        <v>2.5641</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.8759</v>
+        <v>1.3257</v>
       </c>
       <c r="I17" t="n">
-        <v>3.6833</v>
+        <v>1.2384</v>
       </c>
       <c r="J17" t="n">
-        <v>1.6492</v>
+        <v>1.857</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.0634</v>
+        <v>2.135</v>
       </c>
       <c r="L17" t="n">
-        <v>2.7126</v>
+        <v>-0.2781</v>
       </c>
       <c r="M17" t="n">
-        <v>0.1583</v>
+        <v>0.7072000000000001</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.8124</v>
+        <v>-0.8093</v>
       </c>
       <c r="O17" t="n">
-        <v>0.9707</v>
+        <v>1.5165</v>
       </c>
       <c r="P17" t="n">
-        <v>0.3917</v>
+        <v>-0.9792</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9792</v>
+        <v>-2.9377</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3709</v>
+        <v>1.9585</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3251</v>
+        <v>1.1085</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.9328</v>
+        <v>0.5275</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6077</v>
+        <v>0.5809</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.9412</v>
+        <v>-1.3894</v>
       </c>
       <c r="W17" t="n">
-        <v>0.2754</v>
+        <v>-1.114</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.2166</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6042999999999999</v>
+        <v>1.174</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1285</v>
+        <v>0.5377999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4758</v>
+        <v>0.6362</v>
       </c>
       <c r="G18" t="n">
         <v>1.4565</v>
@@ -1858,13 +1858,13 @@
         <v>0.7834</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.9317</v>
+        <v>-0.362</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4158</v>
+        <v>-0.0065</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5159</v>
+        <v>-0.3555</v>
       </c>
       <c r="V18" t="n">
         <v>0.2754</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>I. GRANJA I BERNAD</t>
+          <t>I. JIMENEZ EL MERZOUG</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.1532</v>
+        <v>-2.8841</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.1925</v>
+        <v>-0.5404</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.9607</v>
+        <v>-2.3437</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.641</v>
+        <v>0.1542</v>
       </c>
       <c r="H19" t="n">
-        <v>2.31</v>
+        <v>-0.2804</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.951</v>
+        <v>0.4346</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.3816</v>
+        <v>-0.0041</v>
       </c>
       <c r="K19" t="n">
-        <v>2.3069</v>
+        <v>-0.0137</v>
       </c>
       <c r="L19" t="n">
-        <v>-2.6885</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.2594</v>
+        <v>0.1583</v>
       </c>
       <c r="N19" t="n">
-        <v>0.0031</v>
+        <v>-0.2667</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.2625</v>
+        <v>0.4249</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.5668</v>
+        <v>0.3917</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9585</v>
+        <v>-0.9792</v>
       </c>
       <c r="R19" t="n">
-        <v>0.3917</v>
+        <v>1.3709</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2137</v>
+        <v>0.4952</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1476</v>
+        <v>0.1676</v>
       </c>
       <c r="U19" t="n">
-        <v>0.06610000000000001</v>
+        <v>0.3276</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.159</v>
+        <v>-3.9252</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.2754</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.159</v>
+        <v>-4.2005</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>I. JIMENEZ EL MERZOUG</t>
+          <t>I. GRANJA I BERNAD</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.7598</v>
+        <v>-2.9559</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.3357</v>
+        <v>-2.2948</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.4241</v>
+        <v>-0.661</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1542</v>
+        <v>-0.641</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.2804</v>
+        <v>2.31</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4346</v>
+        <v>-2.951</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.0041</v>
+        <v>-0.3816</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.0137</v>
+        <v>2.3069</v>
       </c>
       <c r="L20" t="n">
-        <v>0.009599999999999999</v>
+        <v>-2.6885</v>
       </c>
       <c r="M20" t="n">
-        <v>0.1583</v>
+        <v>-0.2594</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2667</v>
+        <v>0.0031</v>
       </c>
       <c r="O20" t="n">
-        <v>0.4249</v>
+        <v>-0.2625</v>
       </c>
       <c r="P20" t="n">
+        <v>-1.5668</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>-1.9585</v>
+      </c>
+      <c r="R20" t="n">
         <v>0.3917</v>
       </c>
-      <c r="Q20" t="n">
-        <v>-0.9792</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.3709</v>
-      </c>
       <c r="S20" t="n">
-        <v>-0.3805</v>
+        <v>0.411</v>
       </c>
       <c r="T20" t="n">
-        <v>0.3723</v>
+        <v>0.0453</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.7528</v>
+        <v>0.3657</v>
       </c>
       <c r="V20" t="n">
-        <v>-3.9252</v>
+        <v>-1.159</v>
       </c>
       <c r="W20" t="n">
-        <v>0.2754</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-4.2005</v>
+        <v>-1.159</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.3632</v>
+        <v>-5.0175</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.7822</v>
+        <v>-2.6798</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.581</v>
+        <v>-2.3376</v>
       </c>
       <c r="G21" t="n">
         <v>0.6401</v>
@@ -2092,13 +2092,13 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6704</v>
+        <v>-0.3246</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1782</v>
+        <v>-0.0759</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4921</v>
+        <v>-0.2488</v>
       </c>
       <c r="V21" t="n">
         <v>-3.3745</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>8.442999999999998</v>
+        <v>11.1718</v>
       </c>
       <c r="E22" t="n">
         <v>7.626100000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8168999999999995</v>
+        <v>3.5459</v>
       </c>
       <c r="G22" t="n">
         <v>16.218</v>
@@ -2149,7 +2149,7 @@
         <v>8.8223</v>
       </c>
       <c r="L22" t="n">
-        <v>5.880500000000001</v>
+        <v>5.8805</v>
       </c>
       <c r="M22" t="n">
         <v>1.5152</v>
@@ -2161,7 +2161,7 @@
         <v>5.5618</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.9791000000000003</v>
+        <v>-0.9791000000000007</v>
       </c>
       <c r="Q22" t="n">
         <v>-10.7715</v>
@@ -2170,13 +2170,13 @@
         <v>9.792400000000001</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2645999999999998</v>
+        <v>2.464399999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2176999999999998</v>
+        <v>-0.2177999999999999</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.04679999999999995</v>
+        <v>2.6819</v>
       </c>
       <c r="V22" t="n">
         <v>-6.5312</v>
